--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstMarketManagement001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstMarketManagement001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\WorkSpace\tams_3.0\tams-invest-parent\tams-invest-basicdata\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15216" windowHeight="2508"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15210" windowHeight="2505"/>
   </bookViews>
   <sheets>
     <sheet name="评级变动" sheetId="5" r:id="rId1"/>
@@ -14,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>评级展望</t>
   </si>
@@ -59,13 +64,39 @@
   <si>
     <t>公告日期</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>内评</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.8000000000000007"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.8000000000000007"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>外评</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +123,28 @@
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -150,7 +203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -163,80 +216,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -249,14 +237,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCEDC7"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -291,7 +279,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -326,7 +314,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -535,24 +523,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="10.77734375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -588,11 +576,14 @@
       </c>
       <c r="L1" s="2" t="s">
         <v>2</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>